--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89EABDE-47D2-4DB6-8407-B51989CF139A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113F60A8-B43A-4B24-92E7-501643F71727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="7095" yWindow="2340" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -401,12 +401,6 @@
     <t>soccer_penalty_box_wide_dribbling</t>
   </si>
   <si>
-    <t>soccer_shooting_douple_shooting</t>
-  </si>
-  <si>
-    <t>soccer_shooting_triple_shoooting</t>
-  </si>
-  <si>
     <t>soccer_sprint_one_gate_generic</t>
   </si>
   <si>
@@ -623,9 +617,6 @@
     <t>soccer_yoyo_interm_recover_test_level_2</t>
   </si>
   <si>
-    <t>soccer_five_times_30m_generic</t>
-  </si>
-  <si>
     <t>soccer_five_time_30m_sprint</t>
   </si>
   <si>
@@ -645,6 +636,15 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>soccer_shooting_triple_shooting</t>
+  </si>
+  <si>
+    <t>soccer_shooting_double_shooting</t>
+  </si>
+  <si>
+    <t>soccer_five_time_30m_generic</t>
   </si>
 </sst>
 </file>
@@ -1077,10 +1077,10 @@
         <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1106,10 +1106,10 @@
         <v>77</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1135,10 +1135,10 @@
         <v>77</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1164,10 +1164,10 @@
         <v>77</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1187,10 +1187,10 @@
         <v>77</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1213,13 +1213,13 @@
         <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1245,10 +1245,10 @@
         <v>93</v>
       </c>
       <c r="H8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1274,10 +1274,10 @@
         <v>93</v>
       </c>
       <c r="H9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1303,10 +1303,10 @@
         <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1332,10 +1332,10 @@
         <v>98</v>
       </c>
       <c r="H11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1361,10 +1361,10 @@
         <v>98</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>77</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1448,10 +1448,10 @@
         <v>93</v>
       </c>
       <c r="H15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1477,10 +1477,10 @@
         <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1506,10 +1506,10 @@
         <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I17" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1535,10 +1535,10 @@
         <v>98</v>
       </c>
       <c r="H18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1564,10 +1564,10 @@
         <v>98</v>
       </c>
       <c r="H19" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I19" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1593,10 +1593,10 @@
         <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1622,10 +1622,10 @@
         <v>98</v>
       </c>
       <c r="H21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1651,10 +1651,10 @@
         <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1680,10 +1680,10 @@
         <v>98</v>
       </c>
       <c r="H23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1709,10 +1709,10 @@
         <v>98</v>
       </c>
       <c r="H24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1723,7 +1723,7 @@
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
         <v>82</v>
@@ -1738,10 +1738,10 @@
         <v>98</v>
       </c>
       <c r="H25" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I25" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,7 +1752,7 @@
         <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="D26" t="s">
         <v>82</v>
@@ -1767,10 +1767,10 @@
         <v>98</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I26" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,7 +1789,7 @@
         <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>77</v>
@@ -1801,13 +1801,13 @@
         <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H28" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,7 +1818,7 @@
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
         <v>82</v>
@@ -1833,10 +1833,10 @@
         <v>98</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
         <v>77</v>
@@ -1862,10 +1862,10 @@
         <v>93</v>
       </c>
       <c r="H30" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I30" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1873,10 +1873,10 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
         <v>82</v>
@@ -1891,10 +1891,10 @@
         <v>98</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I31" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,10 +1902,10 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
         <v>77</v>
@@ -1920,10 +1920,10 @@
         <v>98</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I32" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,7 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>82</v>
@@ -1946,13 +1946,13 @@
         <v>88</v>
       </c>
       <c r="G33" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H33" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I33" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1963,22 +1963,22 @@
         <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G34" t="s">
         <v>77</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1994,10 +1994,10 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>82</v>
@@ -2012,10 +2012,10 @@
         <v>93</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2023,10 +2023,10 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>77</v>
@@ -2041,10 +2041,10 @@
         <v>93</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I37" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2052,10 +2052,10 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
         <v>82</v>
@@ -2070,10 +2070,10 @@
         <v>98</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2081,10 +2081,10 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D39" t="s">
         <v>77</v>
@@ -2099,10 +2099,10 @@
         <v>98</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I39" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2110,10 +2110,10 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
         <v>82</v>
@@ -2128,10 +2128,10 @@
         <v>98</v>
       </c>
       <c r="H40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2139,10 +2139,10 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
         <v>77</v>
@@ -2157,10 +2157,10 @@
         <v>98</v>
       </c>
       <c r="H41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I41" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2168,10 +2168,10 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
         <v>82</v>
@@ -2186,10 +2186,10 @@
         <v>98</v>
       </c>
       <c r="H42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I42" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2197,10 +2197,10 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
         <v>77</v>
@@ -2215,10 +2215,10 @@
         <v>98</v>
       </c>
       <c r="H43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I43" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2226,10 +2226,10 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
         <v>82</v>
@@ -2244,10 +2244,10 @@
         <v>93</v>
       </c>
       <c r="H44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I44" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D45" t="s">
         <v>77</v>
@@ -2270,13 +2270,13 @@
         <v>79</v>
       </c>
       <c r="G45" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2284,22 +2284,22 @@
         <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D46" t="s">
         <v>77</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I46" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2307,10 +2307,10 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D47" t="s">
         <v>82</v>
@@ -2325,10 +2325,10 @@
         <v>98</v>
       </c>
       <c r="H47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I47" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2336,10 +2336,10 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
         <v>77</v>
@@ -2354,10 +2354,10 @@
         <v>98</v>
       </c>
       <c r="H48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I48" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2365,10 +2365,10 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D49" t="s">
         <v>82</v>
@@ -2383,10 +2383,10 @@
         <v>98</v>
       </c>
       <c r="H49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I49" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2394,10 +2394,10 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D50" t="s">
         <v>77</v>
@@ -2412,10 +2412,10 @@
         <v>93</v>
       </c>
       <c r="H50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I50" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2423,10 +2423,10 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
         <v>82</v>
@@ -2441,10 +2441,10 @@
         <v>98</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I51" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2452,10 +2452,10 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D52" t="s">
         <v>77</v>
@@ -2470,10 +2470,10 @@
         <v>98</v>
       </c>
       <c r="H52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I52" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
         <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
         <v>77</v>
@@ -2499,10 +2499,10 @@
         <v>98</v>
       </c>
       <c r="H53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I53" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2510,7 +2510,7 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2518,10 +2518,10 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D55" t="s">
         <v>77</v>
@@ -2536,10 +2536,10 @@
         <v>98</v>
       </c>
       <c r="H55" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I55" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2547,10 +2547,10 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D56" t="s">
         <v>82</v>
@@ -2570,10 +2570,10 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
         <v>77</v>
@@ -2588,10 +2588,10 @@
         <v>98</v>
       </c>
       <c r="H57" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2599,7 +2599,7 @@
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2607,16 +2607,16 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
         <v>77</v>
       </c>
       <c r="E59" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F59" t="s">
         <v>79</v>
@@ -2625,10 +2625,10 @@
         <v>77</v>
       </c>
       <c r="H59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I59" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2636,7 +2636,7 @@
         <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D61" t="s">
         <v>77</v>
@@ -2662,10 +2662,10 @@
         <v>98</v>
       </c>
       <c r="H61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I61" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2673,10 +2673,10 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
         <v>77</v>
@@ -2691,10 +2691,10 @@
         <v>98</v>
       </c>
       <c r="H62" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I62" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2702,10 +2702,10 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C63" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D63" t="s">
         <v>77</v>
@@ -2720,10 +2720,10 @@
         <v>98</v>
       </c>
       <c r="H63" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I63" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2731,10 +2731,10 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D64" t="s">
         <v>77</v>
@@ -2749,10 +2749,10 @@
         <v>98</v>
       </c>
       <c r="H64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I64" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2760,10 +2760,10 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D65" t="s">
         <v>77</v>
@@ -2778,10 +2778,10 @@
         <v>93</v>
       </c>
       <c r="H65" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I65" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2789,10 +2789,10 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D66" t="s">
         <v>77</v>
@@ -2807,10 +2807,10 @@
         <v>98</v>
       </c>
       <c r="H66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I66" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2818,7 +2818,7 @@
         <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2826,22 +2826,22 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F68" t="s">
         <v>79</v>
       </c>
       <c r="G68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113F60A8-B43A-4B24-92E7-501643F71727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C90C6F-7294-41E9-93D7-1B0A52A8A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7095" yWindow="2340" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>Soccer Genius Passing and Reveiving</t>
   </si>
   <si>
-    <t>Soccer Genius Accurcy and Finishing</t>
-  </si>
-  <si>
     <t>Soccer Genius Dribbling</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>Accuracy</t>
   </si>
   <si>
-    <t>SG Accurcy and Finishing</t>
-  </si>
-  <si>
     <t>soccer_shooting</t>
   </si>
   <si>
@@ -596,27 +590,15 @@
     <t>YoYo Int. Endurance TL 1 - 5</t>
   </si>
   <si>
-    <t>soccer_yoyo_interm_endurance_test_level_1_5</t>
-  </si>
-  <si>
     <t>YoYo Int. Endurance TL 2 - 5</t>
   </si>
   <si>
-    <t>soccer_yoyo_interm_endurance_test_level_2_5</t>
-  </si>
-  <si>
     <t>YoYo Int. Recovery TL 1 - 10</t>
   </si>
   <si>
-    <t>soccer_yoyo_interm_recover_test_level_1_10</t>
-  </si>
-  <si>
     <t>YoYo Int. Recovery TL 2</t>
   </si>
   <si>
-    <t>soccer_yoyo_interm_recover_test_level_2</t>
-  </si>
-  <si>
     <t>soccer_five_time_30m_sprint</t>
   </si>
   <si>
@@ -645,6 +627,24 @@
   </si>
   <si>
     <t>soccer_five_time_30m_generic</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_recover_test_level_2</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_recover_test_level_1_10</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_endurance_test_level_2_5</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_endurance_test_level_1_5</t>
+  </si>
+  <si>
+    <t>Soccer Genius Accuracy and Finishing</t>
+  </si>
+  <si>
+    <t>SG Accuracy and Finishing</t>
   </si>
 </sst>
 </file>
@@ -1059,28 +1059,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" t="s">
         <v>78</v>
       </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1088,1760 +1088,1760 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>81</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
         <v>82</v>
       </c>
-      <c r="E3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" t="s">
-        <v>83</v>
-      </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
         <v>82</v>
       </c>
-      <c r="E4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" t="s">
-        <v>83</v>
-      </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" t="s">
         <v>86</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" t="s">
         <v>91</v>
       </c>
-      <c r="G8" t="s">
-        <v>93</v>
-      </c>
       <c r="H8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I9" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H11" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I11" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I13" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I14" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I15" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
         <v>78</v>
       </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
         <v>82</v>
       </c>
-      <c r="E17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" t="s">
-        <v>83</v>
-      </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="E18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>83</v>
-      </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I18" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
         <v>82</v>
       </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" t="s">
-        <v>83</v>
-      </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I19" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H21" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I21" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H22" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I22" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I24" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" t="s">
         <v>82</v>
       </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
-      </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I25" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
         <v>82</v>
       </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" t="s">
-        <v>83</v>
-      </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H26" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I26" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H28" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I28" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I29" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" t="s">
         <v>91</v>
       </c>
-      <c r="G30" t="s">
-        <v>93</v>
-      </c>
       <c r="H30" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I30" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I31" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I32" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H33" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I33" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I34" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I36" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" t="s">
         <v>78</v>
       </c>
-      <c r="F37" t="s">
-        <v>79</v>
-      </c>
       <c r="G37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I37" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I38" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E39" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" t="s">
         <v>78</v>
       </c>
-      <c r="F39" t="s">
-        <v>79</v>
-      </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I39" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H40" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I40" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" t="s">
         <v>78</v>
       </c>
-      <c r="F41" t="s">
-        <v>79</v>
-      </c>
       <c r="G41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I41" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G42" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I42" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" t="s">
         <v>78</v>
       </c>
-      <c r="F43" t="s">
-        <v>79</v>
-      </c>
       <c r="G43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I43" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I44" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" t="s">
         <v>78</v>
       </c>
-      <c r="F45" t="s">
-        <v>79</v>
-      </c>
       <c r="G45" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H45" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I45" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E46" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G46" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I46" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F47" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I47" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E48" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" t="s">
         <v>78</v>
       </c>
-      <c r="F48" t="s">
-        <v>79</v>
-      </c>
       <c r="G48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I48" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F49" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H49" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I49" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E50" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" t="s">
         <v>78</v>
       </c>
-      <c r="F50" t="s">
-        <v>79</v>
-      </c>
       <c r="G50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I50" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F51" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G51" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I51" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
+        <v>77</v>
+      </c>
+      <c r="F52" t="s">
         <v>78</v>
       </c>
-      <c r="F52" t="s">
-        <v>79</v>
-      </c>
       <c r="G52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I52" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I53" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E55" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" t="s">
         <v>78</v>
       </c>
-      <c r="F55" t="s">
-        <v>79</v>
-      </c>
       <c r="G55" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H55" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I55" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F56" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E57" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" t="s">
         <v>78</v>
       </c>
-      <c r="F57" t="s">
-        <v>79</v>
-      </c>
       <c r="G57" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I57" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I59" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H61" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I61" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I62" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C63" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I63" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G64" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I64" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G65" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I65" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H66" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I66" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E68" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H68" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I68" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C90C6F-7294-41E9-93D7-1B0A52A8A30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9EAA60-83E2-4BEC-9FB4-4161859BB6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="6345" yWindow="2565" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="203">
   <si>
     <t>title</t>
   </si>
@@ -356,9 +356,6 @@
     <t>soccer_game_action_running</t>
   </si>
   <si>
-    <t>soccer_passing_90dec_passing</t>
-  </si>
-  <si>
     <t>soccer_passing_triple_passing</t>
   </si>
   <si>
@@ -629,22 +626,25 @@
     <t>soccer_five_time_30m_generic</t>
   </si>
   <si>
-    <t>soccer_yoyo_intermittent_recover_test_level_2</t>
-  </si>
-  <si>
-    <t>soccer_yoyo_intermittent_recover_test_level_1_10</t>
-  </si>
-  <si>
-    <t>soccer_yoyo_intermittent_endurance_test_level_2_5</t>
-  </si>
-  <si>
-    <t>soccer_yoyo_intermittent_endurance_test_level_1_5</t>
-  </si>
-  <si>
     <t>Soccer Genius Accuracy and Finishing</t>
   </si>
   <si>
     <t>SG Accuracy and Finishing</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_endurance_level_1</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_endurance_level_2</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_recovery_level_1</t>
+  </si>
+  <si>
+    <t>soccer_yoyo_intermittent_recovery_level_2</t>
+  </si>
+  <si>
+    <t>soccer_passing_90deg_passing</t>
   </si>
 </sst>
 </file>
@@ -1077,10 +1077,10 @@
         <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1106,18 +1106,18 @@
         <v>76</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>83</v>
@@ -1135,10 +1135,10 @@
         <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1164,10 +1164,10 @@
         <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1187,10 +1187,10 @@
         <v>76</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1213,13 +1213,13 @@
         <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1245,10 +1245,10 @@
         <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1274,10 +1274,10 @@
         <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1303,10 +1303,10 @@
         <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1332,10 +1332,10 @@
         <v>96</v>
       </c>
       <c r="H11" t="s">
+        <v>188</v>
+      </c>
+      <c r="I11" t="s">
         <v>189</v>
-      </c>
-      <c r="I11" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1361,10 +1361,10 @@
         <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1390,10 +1390,10 @@
         <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>76</v>
       </c>
       <c r="H14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1448,10 +1448,10 @@
         <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1477,10 +1477,10 @@
         <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1491,7 +1491,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
         <v>81</v>
@@ -1506,10 +1506,10 @@
         <v>96</v>
       </c>
       <c r="H17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1520,7 +1520,7 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>81</v>
@@ -1535,10 +1535,10 @@
         <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>81</v>
@@ -1564,10 +1564,10 @@
         <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1575,10 +1575,10 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
         <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -1593,10 +1593,10 @@
         <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1604,10 +1604,10 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" t="s">
         <v>111</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>81</v>
@@ -1622,10 +1622,10 @@
         <v>96</v>
       </c>
       <c r="H21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1633,10 +1633,10 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
         <v>113</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>81</v>
@@ -1651,10 +1651,10 @@
         <v>96</v>
       </c>
       <c r="H22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1662,10 +1662,10 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
         <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>76</v>
@@ -1680,10 +1680,10 @@
         <v>96</v>
       </c>
       <c r="H23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1691,10 +1691,10 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
         <v>117</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
       </c>
       <c r="D24" t="s">
         <v>81</v>
@@ -1709,10 +1709,10 @@
         <v>96</v>
       </c>
       <c r="H24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1723,7 +1723,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
         <v>81</v>
@@ -1738,10 +1738,10 @@
         <v>96</v>
       </c>
       <c r="H25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,7 +1752,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
         <v>81</v>
@@ -1767,10 +1767,10 @@
         <v>96</v>
       </c>
       <c r="H26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,10 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="G27" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,7 +1792,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>76</v>
@@ -1801,13 +1804,13 @@
         <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,7 +1821,7 @@
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>81</v>
@@ -1833,10 +1836,10 @@
         <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1844,10 +1847,10 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" t="s">
         <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>123</v>
       </c>
       <c r="D30" t="s">
         <v>76</v>
@@ -1862,10 +1865,10 @@
         <v>91</v>
       </c>
       <c r="H30" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" t="s">
         <v>189</v>
-      </c>
-      <c r="I30" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1873,10 +1876,10 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
         <v>124</v>
-      </c>
-      <c r="C31" t="s">
-        <v>125</v>
       </c>
       <c r="D31" t="s">
         <v>81</v>
@@ -1891,10 +1894,10 @@
         <v>96</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,10 +1905,10 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" t="s">
         <v>126</v>
-      </c>
-      <c r="C32" t="s">
-        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>76</v>
@@ -1920,10 +1923,10 @@
         <v>96</v>
       </c>
       <c r="H32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1934,7 +1937,7 @@
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
         <v>81</v>
@@ -1946,13 +1949,13 @@
         <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1963,22 +1966,22 @@
         <v>40</v>
       </c>
       <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" t="s">
         <v>129</v>
       </c>
-      <c r="D34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>130</v>
-      </c>
       <c r="G34" t="s">
         <v>76</v>
       </c>
       <c r="H34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1986,7 +1989,10 @@
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+      <c r="G35" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1994,10 +2000,10 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" t="s">
         <v>133</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
       </c>
       <c r="D36" t="s">
         <v>81</v>
@@ -2012,10 +2018,10 @@
         <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2023,10 +2029,10 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" t="s">
         <v>135</v>
-      </c>
-      <c r="C37" t="s">
-        <v>136</v>
       </c>
       <c r="D37" t="s">
         <v>76</v>
@@ -2041,10 +2047,10 @@
         <v>91</v>
       </c>
       <c r="H37" t="s">
+        <v>188</v>
+      </c>
+      <c r="I37" t="s">
         <v>189</v>
-      </c>
-      <c r="I37" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2052,10 +2058,10 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" t="s">
         <v>137</v>
-      </c>
-      <c r="C38" t="s">
-        <v>138</v>
       </c>
       <c r="D38" t="s">
         <v>81</v>
@@ -2070,10 +2076,10 @@
         <v>96</v>
       </c>
       <c r="H38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2081,10 +2087,10 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
         <v>139</v>
-      </c>
-      <c r="C39" t="s">
-        <v>140</v>
       </c>
       <c r="D39" t="s">
         <v>76</v>
@@ -2099,10 +2105,10 @@
         <v>96</v>
       </c>
       <c r="H39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2110,10 +2116,10 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" t="s">
         <v>141</v>
-      </c>
-      <c r="C40" t="s">
-        <v>142</v>
       </c>
       <c r="D40" t="s">
         <v>81</v>
@@ -2128,10 +2134,10 @@
         <v>96</v>
       </c>
       <c r="H40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2139,10 +2145,10 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" t="s">
         <v>143</v>
-      </c>
-      <c r="C41" t="s">
-        <v>144</v>
       </c>
       <c r="D41" t="s">
         <v>76</v>
@@ -2157,10 +2163,10 @@
         <v>96</v>
       </c>
       <c r="H41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2168,10 +2174,10 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" t="s">
         <v>145</v>
-      </c>
-      <c r="C42" t="s">
-        <v>146</v>
       </c>
       <c r="D42" t="s">
         <v>81</v>
@@ -2186,10 +2192,10 @@
         <v>96</v>
       </c>
       <c r="H42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2197,10 +2203,10 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" t="s">
         <v>147</v>
-      </c>
-      <c r="C43" t="s">
-        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>76</v>
@@ -2215,10 +2221,10 @@
         <v>96</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2226,10 +2232,10 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" t="s">
         <v>149</v>
-      </c>
-      <c r="C44" t="s">
-        <v>150</v>
       </c>
       <c r="D44" t="s">
         <v>81</v>
@@ -2244,10 +2250,10 @@
         <v>91</v>
       </c>
       <c r="H44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2255,10 +2261,10 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" t="s">
-        <v>152</v>
       </c>
       <c r="D45" t="s">
         <v>76</v>
@@ -2270,13 +2276,13 @@
         <v>78</v>
       </c>
       <c r="G45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2284,22 +2290,22 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" t="s">
         <v>153</v>
       </c>
-      <c r="D46" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" t="s">
-        <v>154</v>
-      </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2307,10 +2313,10 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" t="s">
         <v>155</v>
-      </c>
-      <c r="C47" t="s">
-        <v>156</v>
       </c>
       <c r="D47" t="s">
         <v>81</v>
@@ -2325,10 +2331,10 @@
         <v>96</v>
       </c>
       <c r="H47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2336,10 +2342,10 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" t="s">
         <v>157</v>
-      </c>
-      <c r="C48" t="s">
-        <v>158</v>
       </c>
       <c r="D48" t="s">
         <v>76</v>
@@ -2354,10 +2360,10 @@
         <v>96</v>
       </c>
       <c r="H48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2365,10 +2371,10 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" t="s">
         <v>159</v>
-      </c>
-      <c r="C49" t="s">
-        <v>160</v>
       </c>
       <c r="D49" t="s">
         <v>81</v>
@@ -2383,10 +2389,10 @@
         <v>96</v>
       </c>
       <c r="H49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2394,10 +2400,10 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
         <v>161</v>
-      </c>
-      <c r="C50" t="s">
-        <v>162</v>
       </c>
       <c r="D50" t="s">
         <v>76</v>
@@ -2412,10 +2418,10 @@
         <v>91</v>
       </c>
       <c r="H50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2423,10 +2429,10 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
         <v>163</v>
-      </c>
-      <c r="C51" t="s">
-        <v>164</v>
       </c>
       <c r="D51" t="s">
         <v>81</v>
@@ -2441,10 +2447,10 @@
         <v>96</v>
       </c>
       <c r="H51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2452,10 +2458,10 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
         <v>165</v>
-      </c>
-      <c r="C52" t="s">
-        <v>166</v>
       </c>
       <c r="D52" t="s">
         <v>76</v>
@@ -2470,10 +2476,10 @@
         <v>96</v>
       </c>
       <c r="H52" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2484,7 +2490,7 @@
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
         <v>76</v>
@@ -2499,10 +2505,10 @@
         <v>96</v>
       </c>
       <c r="H53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2510,7 +2516,10 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="G54" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2518,10 +2527,10 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" t="s">
         <v>169</v>
-      </c>
-      <c r="C55" t="s">
-        <v>170</v>
       </c>
       <c r="D55" t="s">
         <v>76</v>
@@ -2536,10 +2545,10 @@
         <v>96</v>
       </c>
       <c r="H55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2547,10 +2556,10 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s">
         <v>171</v>
-      </c>
-      <c r="C56" t="s">
-        <v>172</v>
       </c>
       <c r="D56" t="s">
         <v>81</v>
@@ -2570,10 +2579,10 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" t="s">
         <v>173</v>
-      </c>
-      <c r="C57" t="s">
-        <v>174</v>
       </c>
       <c r="D57" t="s">
         <v>76</v>
@@ -2588,10 +2597,10 @@
         <v>96</v>
       </c>
       <c r="H57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2599,7 +2608,10 @@
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="G58" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2607,16 +2619,16 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
         <v>176</v>
       </c>
-      <c r="C59" t="s">
-        <v>177</v>
-      </c>
       <c r="D59" t="s">
         <v>76</v>
       </c>
       <c r="E59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F59" t="s">
         <v>78</v>
@@ -2625,10 +2637,10 @@
         <v>76</v>
       </c>
       <c r="H59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I59" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2636,7 +2648,10 @@
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+      <c r="G60" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2644,10 +2659,10 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" t="s">
         <v>179</v>
-      </c>
-      <c r="C61" t="s">
-        <v>180</v>
       </c>
       <c r="D61" t="s">
         <v>76</v>
@@ -2662,10 +2677,10 @@
         <v>96</v>
       </c>
       <c r="H61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2673,10 +2688,10 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
         <v>181</v>
-      </c>
-      <c r="C62" t="s">
-        <v>182</v>
       </c>
       <c r="D62" t="s">
         <v>76</v>
@@ -2691,10 +2706,10 @@
         <v>96</v>
       </c>
       <c r="H62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2702,10 +2717,10 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D63" t="s">
         <v>76</v>
@@ -2720,10 +2735,10 @@
         <v>96</v>
       </c>
       <c r="H63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2731,7 +2746,7 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C64" t="s">
         <v>199</v>
@@ -2749,10 +2764,10 @@
         <v>96</v>
       </c>
       <c r="H64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I64" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2760,10 +2775,10 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D65" t="s">
         <v>76</v>
@@ -2778,10 +2793,10 @@
         <v>91</v>
       </c>
       <c r="H65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2789,10 +2804,10 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
         <v>76</v>
@@ -2807,10 +2822,10 @@
         <v>96</v>
       </c>
       <c r="H66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I66" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2818,7 +2833,10 @@
         <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>195</v>
+      </c>
+      <c r="G67" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2826,22 +2844,22 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F68" t="s">
         <v>78</v>
       </c>
       <c r="G68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I68" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9EAA60-83E2-4BEC-9FB4-4161859BB6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AABE33D-7259-4781-8E8B-67D77D864DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="2565" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="193">
   <si>
     <t>title</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Triple shooting</t>
   </si>
   <si>
-    <t>One Gate Generic</t>
-  </si>
-  <si>
     <t>T-Test</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Y-Test</t>
   </si>
   <si>
-    <t>Two Gates Exit Two Generic</t>
-  </si>
-  <si>
     <t>10 meters dribbling</t>
   </si>
   <si>
@@ -218,9 +212,6 @@
     <t>Illinois agility</t>
   </si>
   <si>
-    <t>Three Gates Exit Three Generic</t>
-  </si>
-  <si>
     <t>30 meters sprint with 10 meters lab</t>
   </si>
   <si>
@@ -230,9 +221,6 @@
     <t>10 meters sprint with 5 meters lap</t>
   </si>
   <si>
-    <t>Four Gates Exit Four Generic</t>
-  </si>
-  <si>
     <t>30 m sprint / 20m and 10 m lap</t>
   </si>
   <si>
@@ -392,9 +380,6 @@
     <t>soccer_penalty_box_wide_dribbling</t>
   </si>
   <si>
-    <t>soccer_sprint_one_gate_generic</t>
-  </si>
-  <si>
     <t>soccer_t_test</t>
   </si>
   <si>
@@ -428,9 +413,6 @@
     <t>Not used</t>
   </si>
   <si>
-    <t>soccer_sprint_two_gates_exit_two_generic</t>
-  </si>
-  <si>
     <t>Na</t>
   </si>
   <si>
@@ -539,9 +521,6 @@
     <t>soccer_illinois_agility</t>
   </si>
   <si>
-    <t>soccer_sprint_three_gates_exit_three_generic</t>
-  </si>
-  <si>
     <t>30 m sprint / 10 m lab</t>
   </si>
   <si>
@@ -560,18 +539,12 @@
     <t>soccer_10m_sprint_with_5m_lap</t>
   </si>
   <si>
-    <t>soccer_sprint_four_gates_exit_four_generic</t>
-  </si>
-  <si>
     <t>30 m sprint / 20m &amp; 10 m lap</t>
   </si>
   <si>
     <t>soccer_30m_sprint_with_20m_and_10m_lap</t>
   </si>
   <si>
-    <t>soccer_endurance_generic</t>
-  </si>
-  <si>
     <t>YoYo Endurance TL 1</t>
   </si>
   <si>
@@ -621,9 +594,6 @@
   </si>
   <si>
     <t>soccer_shooting_double_shooting</t>
-  </si>
-  <si>
-    <t>soccer_five_time_30m_generic</t>
   </si>
   <si>
     <t>Soccer Genius Accuracy and Finishing</t>
@@ -1016,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204655E-E80D-446C-AF0B-3E0CCA1683CF}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
@@ -1059,28 +1029,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" t="s">
-        <v>78</v>
-      </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1088,57 +1058,57 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1146,28 +1116,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1175,22 +1145,22 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I6" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1201,25 +1171,25 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1230,25 +1200,25 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I8" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1256,28 +1226,28 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1285,28 +1255,28 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1314,28 +1284,28 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1346,25 +1316,25 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I12" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1372,28 +1342,28 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I13" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1401,28 +1371,28 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1433,25 +1403,25 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1462,25 +1432,25 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1491,25 +1461,25 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1520,25 +1490,25 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I18" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,25 +1519,25 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I19" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1575,28 +1545,28 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I20" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1604,28 +1574,28 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I21" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1633,28 +1603,28 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I22" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1662,28 +1632,28 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I23" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1691,28 +1661,28 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I24" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1723,25 +1693,25 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I25" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,36 +1722,54 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I26" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="D27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>183</v>
+      </c>
+      <c r="H27" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,25 +1780,25 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="I28" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,28 +1806,28 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I29" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1847,28 +1835,28 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="I30" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1876,28 +1864,28 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I31" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1905,28 +1893,28 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="I32" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1937,25 +1925,22 @@
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="I33" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1963,36 +1948,57 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>73</v>
+      </c>
+      <c r="F34" t="s">
+        <v>82</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I34" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>41</v>
       </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" t="s">
+        <v>74</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="H35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2000,28 +2006,28 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="I36" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2029,28 +2035,28 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="I37" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2058,28 +2064,28 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="I38" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2087,28 +2093,28 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I39" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2116,28 +2122,28 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="I40" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2145,28 +2151,28 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I41" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2174,28 +2180,28 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I42" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2203,57 +2209,51 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G43" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I43" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>50</v>
       </c>
-      <c r="B44" t="s">
-        <v>148</v>
-      </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="G44" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I44" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2261,51 +2261,57 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F45" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I45" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>52</v>
       </c>
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
-        <v>153</v>
+        <v>73</v>
+      </c>
+      <c r="F46" t="s">
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I46" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2313,28 +2319,28 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I47" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2342,28 +2348,28 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F48" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I48" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2371,28 +2377,28 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F49" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I49" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2400,28 +2406,28 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I50" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2429,28 +2435,28 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I51" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2458,28 +2464,28 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G52" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I52" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2487,39 +2493,51 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s">
-        <v>96</v>
-      </c>
-      <c r="H53" t="s">
-        <v>131</v>
-      </c>
-      <c r="I53" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>60</v>
       </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="D54" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" t="s">
+        <v>74</v>
       </c>
       <c r="G54" t="s">
-        <v>76</v>
+        <v>92</v>
+      </c>
+      <c r="H54" t="s">
+        <v>125</v>
+      </c>
+      <c r="I54" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2527,339 +2545,225 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
         <v>168</v>
       </c>
-      <c r="C55" t="s">
-        <v>169</v>
-      </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E55" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H55" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I55" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" t="s">
+        <v>170</v>
+      </c>
+      <c r="D56" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" t="s">
         <v>62</v>
       </c>
-      <c r="B56" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" t="s">
-        <v>171</v>
-      </c>
-      <c r="D56" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56" t="s">
-        <v>86</v>
-      </c>
       <c r="G56" t="s">
-        <v>76</v>
+        <v>92</v>
+      </c>
+      <c r="H56" t="s">
+        <v>125</v>
+      </c>
+      <c r="I56" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="s">
         <v>172</v>
       </c>
-      <c r="C57" t="s">
-        <v>173</v>
-      </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F57" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G57" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I57" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>188</v>
+      </c>
+      <c r="D58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58" t="s">
+        <v>62</v>
       </c>
       <c r="G58" t="s">
-        <v>76</v>
+        <v>92</v>
+      </c>
+      <c r="H58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E59" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="F59" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G59" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H59" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I59" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="B60" t="s">
+        <v>175</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>190</v>
+      </c>
+      <c r="D60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" t="s">
+        <v>62</v>
       </c>
       <c r="G60" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="H60" t="s">
+        <v>125</v>
+      </c>
+      <c r="I60" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E61" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G61" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H61" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I61" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
-      </c>
-      <c r="D62" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="E62" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="F62" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G62" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="H62" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I62" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" t="s">
         <v>182</v>
-      </c>
-      <c r="C63" t="s">
-        <v>198</v>
-      </c>
-      <c r="D63" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" t="s">
-        <v>77</v>
-      </c>
-      <c r="F63" t="s">
-        <v>66</v>
-      </c>
-      <c r="G63" t="s">
-        <v>96</v>
-      </c>
-      <c r="H63" t="s">
-        <v>131</v>
-      </c>
-      <c r="I63" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" t="s">
-        <v>183</v>
-      </c>
-      <c r="C64" t="s">
-        <v>199</v>
-      </c>
-      <c r="D64" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" t="s">
-        <v>77</v>
-      </c>
-      <c r="F64" t="s">
-        <v>66</v>
-      </c>
-      <c r="G64" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" t="s">
-        <v>131</v>
-      </c>
-      <c r="I64" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" t="s">
-        <v>184</v>
-      </c>
-      <c r="C65" t="s">
-        <v>200</v>
-      </c>
-      <c r="D65" t="s">
-        <v>76</v>
-      </c>
-      <c r="E65" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G65" t="s">
-        <v>91</v>
-      </c>
-      <c r="H65" t="s">
-        <v>131</v>
-      </c>
-      <c r="I65" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" t="s">
-        <v>185</v>
-      </c>
-      <c r="C66" t="s">
-        <v>201</v>
-      </c>
-      <c r="D66" t="s">
-        <v>76</v>
-      </c>
-      <c r="E66" t="s">
-        <v>77</v>
-      </c>
-      <c r="F66" t="s">
-        <v>66</v>
-      </c>
-      <c r="G66" t="s">
-        <v>96</v>
-      </c>
-      <c r="H66" t="s">
-        <v>131</v>
-      </c>
-      <c r="I66" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>73</v>
-      </c>
-      <c r="C67" t="s">
-        <v>195</v>
-      </c>
-      <c r="G67" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F68" t="s">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s">
-        <v>187</v>
-      </c>
-      <c r="H68" t="s">
-        <v>131</v>
-      </c>
-      <c r="I68" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AABE33D-7259-4781-8E8B-67D77D864DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA60187-614B-4CBC-AB5C-D746FE7D08B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="192">
   <si>
     <t>title</t>
   </si>
@@ -570,9 +570,6 @@
   </si>
   <si>
     <t>soccer_five_time_30m_sprint</t>
-  </si>
-  <si>
-    <t>Not available</t>
   </si>
   <si>
     <t>Premium</t>
@@ -1050,7 +1047,7 @@
         <v>125</v>
       </c>
       <c r="I2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1079,15 +1076,15 @@
         <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
         <v>186</v>
-      </c>
-      <c r="B4" t="s">
-        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
@@ -1108,7 +1105,7 @@
         <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1137,7 +1134,7 @@
         <v>125</v>
       </c>
       <c r="I5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1160,7 +1157,7 @@
         <v>125</v>
       </c>
       <c r="I6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1183,13 +1180,13 @@
         <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1215,10 +1212,10 @@
         <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1244,10 +1241,10 @@
         <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1276,7 +1273,7 @@
         <v>125</v>
       </c>
       <c r="I10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1302,10 +1299,10 @@
         <v>92</v>
       </c>
       <c r="H11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" t="s">
         <v>179</v>
-      </c>
-      <c r="I11" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1334,7 +1331,7 @@
         <v>125</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1363,7 +1360,7 @@
         <v>125</v>
       </c>
       <c r="I13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1392,7 +1389,7 @@
         <v>125</v>
       </c>
       <c r="I14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1418,10 +1415,10 @@
         <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1447,10 +1444,10 @@
         <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1461,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
         <v>77</v>
@@ -1476,10 +1473,10 @@
         <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1505,10 +1502,10 @@
         <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1534,10 +1531,10 @@
         <v>92</v>
       </c>
       <c r="H19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,10 +1560,10 @@
         <v>92</v>
       </c>
       <c r="H20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1592,10 +1589,10 @@
         <v>92</v>
       </c>
       <c r="H21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1621,10 +1618,10 @@
         <v>92</v>
       </c>
       <c r="H22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1650,10 +1647,10 @@
         <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1679,10 +1676,10 @@
         <v>92</v>
       </c>
       <c r="H24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1693,7 +1690,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
         <v>77</v>
@@ -1708,10 +1705,10 @@
         <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1722,7 +1719,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D26" t="s">
         <v>77</v>
@@ -1737,10 +1734,10 @@
         <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,13 +1760,13 @@
         <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1795,7 @@
         <v>125</v>
       </c>
       <c r="I28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1824,10 +1821,10 @@
         <v>87</v>
       </c>
       <c r="H29" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" t="s">
         <v>179</v>
-      </c>
-      <c r="I29" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1856,7 +1853,7 @@
         <v>125</v>
       </c>
       <c r="I30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1885,7 +1882,7 @@
         <v>125</v>
       </c>
       <c r="I31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1908,13 +1905,13 @@
         <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1966,10 +1963,10 @@
         <v>87</v>
       </c>
       <c r="H34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1995,10 +1992,10 @@
         <v>87</v>
       </c>
       <c r="H35" t="s">
+        <v>178</v>
+      </c>
+      <c r="I35" t="s">
         <v>179</v>
-      </c>
-      <c r="I35" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2027,7 +2024,7 @@
         <v>125</v>
       </c>
       <c r="I36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2056,7 +2053,7 @@
         <v>125</v>
       </c>
       <c r="I37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2082,10 +2079,10 @@
         <v>92</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2114,7 +2111,7 @@
         <v>125</v>
       </c>
       <c r="I39" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2143,7 +2140,7 @@
         <v>125</v>
       </c>
       <c r="I40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2172,7 +2169,7 @@
         <v>125</v>
       </c>
       <c r="I41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2201,7 +2198,7 @@
         <v>125</v>
       </c>
       <c r="I42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2224,13 +2221,13 @@
         <v>74</v>
       </c>
       <c r="G43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H43" t="s">
         <v>125</v>
       </c>
       <c r="I43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2247,13 +2244,13 @@
         <v>147</v>
       </c>
       <c r="G44" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="H44" t="s">
         <v>125</v>
       </c>
       <c r="I44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2282,7 +2279,7 @@
         <v>125</v>
       </c>
       <c r="I45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2311,7 +2308,7 @@
         <v>125</v>
       </c>
       <c r="I46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2340,7 +2337,7 @@
         <v>125</v>
       </c>
       <c r="I47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2369,7 +2366,7 @@
         <v>125</v>
       </c>
       <c r="I48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2398,7 +2395,7 @@
         <v>125</v>
       </c>
       <c r="I49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2427,7 +2424,7 @@
         <v>125</v>
       </c>
       <c r="I50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2456,7 +2453,7 @@
         <v>125</v>
       </c>
       <c r="I51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2485,7 +2482,7 @@
         <v>125</v>
       </c>
       <c r="I52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2537,7 +2534,7 @@
         <v>125</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2566,7 +2563,7 @@
         <v>125</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2595,7 +2592,7 @@
         <v>125</v>
       </c>
       <c r="I56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2624,7 +2621,7 @@
         <v>125</v>
       </c>
       <c r="I57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2635,7 +2632,7 @@
         <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D58" t="s">
         <v>72</v>
@@ -2653,7 +2650,7 @@
         <v>125</v>
       </c>
       <c r="I58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2664,7 +2661,7 @@
         <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
         <v>72</v>
@@ -2682,7 +2679,7 @@
         <v>125</v>
       </c>
       <c r="I59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2693,7 +2690,7 @@
         <v>175</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D60" t="s">
         <v>72</v>
@@ -2711,7 +2708,7 @@
         <v>125</v>
       </c>
       <c r="I60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2722,7 +2719,7 @@
         <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D61" t="s">
         <v>72</v>
@@ -2740,7 +2737,7 @@
         <v>125</v>
       </c>
       <c r="I61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2757,13 +2754,13 @@
         <v>74</v>
       </c>
       <c r="G62" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="H62" t="s">
         <v>125</v>
       </c>
       <c r="I62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA60187-614B-4CBC-AB5C-D746FE7D08B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439E915-68C5-4241-AF53-302694177B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="-21720" yWindow="2205" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,9 +68,6 @@
     <t>Soccer Genius Game Action Running</t>
   </si>
   <si>
-    <t>Soccer Genius Passing and Reveiving</t>
-  </si>
-  <si>
     <t>Soccer Genius Dribbling</t>
   </si>
   <si>
@@ -612,6 +609,9 @@
   </si>
   <si>
     <t>soccer_passing_90deg_passing</t>
+  </si>
+  <si>
+    <t>Soccer Genius Passing and Receiving</t>
   </si>
 </sst>
 </file>
@@ -1026,1741 +1026,1741 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
         <v>70</v>
       </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
         <v>73</v>
       </c>
-      <c r="F2" t="s">
-        <v>74</v>
-      </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
       <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
         <v>77</v>
       </c>
-      <c r="E3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" t="s">
         <v>185</v>
       </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" t="s">
         <v>77</v>
       </c>
-      <c r="E4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" t="s">
-        <v>78</v>
-      </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
         <v>80</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" t="s">
-        <v>82</v>
-      </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" t="s">
         <v>84</v>
       </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>85</v>
-      </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
         <v>86</v>
       </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" t="s">
-        <v>87</v>
-      </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
         <v>88</v>
       </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
         <v>90</v>
       </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s">
         <v>93</v>
       </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" t="s">
         <v>178</v>
-      </c>
-      <c r="I11" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" t="s">
         <v>96</v>
       </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
         <v>98</v>
       </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
         <v>73</v>
       </c>
-      <c r="F16" t="s">
-        <v>74</v>
-      </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
         <v>77</v>
       </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" t="s">
-        <v>78</v>
-      </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
         <v>77</v>
       </c>
-      <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
         <v>77</v>
       </c>
-      <c r="E19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" t="s">
-        <v>78</v>
-      </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
         <v>104</v>
       </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
         <v>106</v>
       </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
         <v>108</v>
       </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
         <v>110</v>
       </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
         <v>112</v>
       </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" t="s">
         <v>77</v>
       </c>
-      <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" t="s">
-        <v>78</v>
-      </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" t="s">
         <v>77</v>
       </c>
-      <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" t="s">
-        <v>78</v>
-      </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
         <v>116</v>
       </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" t="s">
         <v>178</v>
-      </c>
-      <c r="I29" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
         <v>118</v>
       </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
         <v>120</v>
       </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" t="s">
         <v>123</v>
       </c>
-      <c r="D33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" t="s">
-        <v>124</v>
-      </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
         <v>126</v>
       </c>
-      <c r="C34" t="s">
-        <v>127</v>
-      </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
         <v>128</v>
       </c>
-      <c r="C35" t="s">
-        <v>129</v>
-      </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E35" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" t="s">
         <v>73</v>
       </c>
-      <c r="F35" t="s">
-        <v>74</v>
-      </c>
       <c r="G35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
+        <v>177</v>
+      </c>
+      <c r="I35" t="s">
         <v>178</v>
-      </c>
-      <c r="I35" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
         <v>130</v>
       </c>
-      <c r="C36" t="s">
-        <v>131</v>
-      </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
         <v>132</v>
       </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" t="s">
-        <v>74</v>
-      </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
         <v>134</v>
       </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" t="s">
         <v>136</v>
       </c>
-      <c r="C39" t="s">
-        <v>137</v>
-      </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" t="s">
         <v>73</v>
       </c>
-      <c r="F39" t="s">
-        <v>74</v>
-      </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
         <v>138</v>
       </c>
-      <c r="C40" t="s">
-        <v>139</v>
-      </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" t="s">
         <v>140</v>
       </c>
-      <c r="C41" t="s">
-        <v>141</v>
-      </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E41" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" t="s">
         <v>73</v>
       </c>
-      <c r="F41" t="s">
-        <v>74</v>
-      </c>
       <c r="G41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" t="s">
         <v>142</v>
       </c>
-      <c r="C42" t="s">
-        <v>143</v>
-      </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
         <v>144</v>
       </c>
-      <c r="C43" t="s">
-        <v>145</v>
-      </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
         <v>73</v>
       </c>
-      <c r="F43" t="s">
-        <v>74</v>
-      </c>
       <c r="G43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" t="s">
         <v>146</v>
       </c>
-      <c r="D44" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" t="s">
-        <v>147</v>
-      </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s">
         <v>148</v>
       </c>
-      <c r="C45" t="s">
-        <v>149</v>
-      </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
         <v>150</v>
       </c>
-      <c r="C46" t="s">
-        <v>151</v>
-      </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" t="s">
         <v>73</v>
       </c>
-      <c r="F46" t="s">
-        <v>74</v>
-      </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
         <v>152</v>
       </c>
-      <c r="C47" t="s">
-        <v>153</v>
-      </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
         <v>154</v>
       </c>
-      <c r="C48" t="s">
-        <v>155</v>
-      </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E48" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" t="s">
         <v>73</v>
       </c>
-      <c r="F48" t="s">
-        <v>74</v>
-      </c>
       <c r="G48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" t="s">
         <v>156</v>
       </c>
-      <c r="C49" t="s">
-        <v>157</v>
-      </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" t="s">
         <v>158</v>
       </c>
-      <c r="C50" t="s">
-        <v>159</v>
-      </c>
       <c r="D50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" t="s">
+        <v>72</v>
+      </c>
+      <c r="F50" t="s">
         <v>73</v>
       </c>
-      <c r="F50" t="s">
-        <v>74</v>
-      </c>
       <c r="G50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" t="s">
         <v>161</v>
       </c>
-      <c r="C52" t="s">
-        <v>162</v>
-      </c>
       <c r="D52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" t="s">
         <v>73</v>
       </c>
-      <c r="F52" t="s">
-        <v>74</v>
-      </c>
       <c r="G52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" t="s">
         <v>163</v>
       </c>
-      <c r="C53" t="s">
-        <v>164</v>
-      </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s">
         <v>165</v>
       </c>
-      <c r="C54" t="s">
-        <v>166</v>
-      </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" t="s">
         <v>73</v>
       </c>
-      <c r="F54" t="s">
-        <v>74</v>
-      </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s">
         <v>167</v>
       </c>
-      <c r="C55" t="s">
-        <v>168</v>
-      </c>
       <c r="D55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E55" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" t="s">
         <v>169</v>
       </c>
-      <c r="C56" t="s">
-        <v>170</v>
-      </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
         <v>171</v>
       </c>
-      <c r="C57" t="s">
-        <v>172</v>
-      </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439E915-68C5-4241-AF53-302694177B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E69D397-AFA0-4930-A542-447A02D1D3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="2205" windowWidth="16410" windowHeight="11295" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="28680" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="195">
   <si>
     <t>title</t>
   </si>
@@ -612,6 +612,15 @@
   </si>
   <si>
     <t>Soccer Genius Passing and Receiving</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>video</t>
   </si>
 </sst>
 </file>
@@ -983,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204655E-E80D-446C-AF0B-3E0CCA1683CF}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
@@ -992,7 +1001,7 @@
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1020,8 +1029,17 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1049,8 +1067,17 @@
       <c r="I2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -1078,8 +1105,17 @@
       <c r="I3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>184</v>
       </c>
@@ -1107,8 +1143,17 @@
       <c r="I4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1136,8 +1181,17 @@
       <c r="I5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1159,8 +1213,17 @@
       <c r="I6" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1188,8 +1251,17 @@
       <c r="I7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1217,8 +1289,17 @@
       <c r="I8" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1246,8 +1327,17 @@
       <c r="I9" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1275,8 +1365,17 @@
       <c r="I10" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1304,8 +1403,17 @@
       <c r="I11" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1333,8 +1441,17 @@
       <c r="I12" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1362,8 +1479,17 @@
       <c r="I13" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1391,8 +1517,17 @@
       <c r="I14" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1420,8 +1555,17 @@
       <c r="I15" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1449,8 +1593,17 @@
       <c r="I16" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1478,8 +1631,17 @@
       <c r="I17" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1669,17 @@
       <c r="I18" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1536,8 +1707,17 @@
       <c r="I19" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1565,8 +1745,17 @@
       <c r="I20" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1594,8 +1783,17 @@
       <c r="I21" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1623,8 +1821,17 @@
       <c r="I22" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1652,8 +1859,17 @@
       <c r="I23" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1681,8 +1897,17 @@
       <c r="I24" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1710,8 +1935,17 @@
       <c r="I25" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1739,8 +1973,17 @@
       <c r="I26" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1768,8 +2011,17 @@
       <c r="I27" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1797,8 +2049,17 @@
       <c r="I28" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1826,8 +2087,17 @@
       <c r="I29" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1855,8 +2125,17 @@
       <c r="I30" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1884,8 +2163,17 @@
       <c r="I31" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1913,8 +2201,17 @@
       <c r="I32" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1939,8 +2236,17 @@
       <c r="I33" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1968,8 +2274,17 @@
       <c r="I34" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1997,8 +2312,17 @@
       <c r="I35" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2026,8 +2350,17 @@
       <c r="I36" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2055,8 +2388,17 @@
       <c r="I37" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2084,8 +2426,17 @@
       <c r="I38" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -2113,8 +2464,17 @@
       <c r="I39" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2142,8 +2502,17 @@
       <c r="I40" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -2171,8 +2540,17 @@
       <c r="I41" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2200,8 +2578,17 @@
       <c r="I42" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -2229,8 +2616,17 @@
       <c r="I43" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -2252,8 +2648,17 @@
       <c r="I44" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2281,8 +2686,17 @@
       <c r="I45" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -2310,8 +2724,17 @@
       <c r="I46" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -2339,8 +2762,17 @@
       <c r="I47" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -2368,8 +2800,17 @@
       <c r="I48" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2397,8 +2838,17 @@
       <c r="I49" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -2426,8 +2876,17 @@
       <c r="I50" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -2455,8 +2914,17 @@
       <c r="I51" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -2484,8 +2952,17 @@
       <c r="I52" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -2507,8 +2984,17 @@
       <c r="G53" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -2536,8 +3022,17 @@
       <c r="I54" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -2565,8 +3060,17 @@
       <c r="I55" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -2594,8 +3098,17 @@
       <c r="I56" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -2623,8 +3136,17 @@
       <c r="I57" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -2652,8 +3174,17 @@
       <c r="I58" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -2681,8 +3212,17 @@
       <c r="I59" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -2710,8 +3250,17 @@
       <c r="I60" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -2739,8 +3288,17 @@
       <c r="I61" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -2761,6 +3319,15 @@
       </c>
       <c r="I62" t="s">
         <v>180</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E69D397-AFA0-4930-A542-447A02D1D3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4C67ED-35B4-4A96-9FA3-AF678443859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="-28905" yWindow="3135" windowWidth="14610" windowHeight="15585" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="196">
   <si>
     <t>title</t>
   </si>
@@ -581,9 +581,6 @@
     <t>Professional</t>
   </si>
   <si>
-    <t>Key</t>
-  </si>
-  <si>
     <t>soccer_shooting_triple_shooting</t>
   </si>
   <si>
@@ -621,6 +618,12 @@
   </si>
   <si>
     <t>video</t>
+  </si>
+  <si>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>IDP Key</t>
   </si>
 </sst>
 </file>
@@ -656,7 +659,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -992,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204655E-E80D-446C-AF0B-3E0CCA1683CF}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
@@ -1001,2333 +1005,3077 @@
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="O1" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" t="s">
         <v>184</v>
       </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G7" t="s">
-        <v>181</v>
-      </c>
-      <c r="H7" t="s">
-        <v>177</v>
-      </c>
-      <c r="I7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>4</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I8" t="s">
-        <v>177</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K8" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>4</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>89</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H11" t="s">
-        <v>177</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I12" t="s">
-        <v>177</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I13" t="s">
-        <v>177</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I14" t="s">
-        <v>177</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>3</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>2</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
+        <v>4</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H17" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" t="s">
-        <v>177</v>
-      </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
+        <v>3</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="b">
+      <c r="L18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O18" s="1">
+        <v>2</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H19" t="s">
-        <v>177</v>
-      </c>
-      <c r="I19" t="s">
-        <v>177</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="b">
+      <c r="J19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O19" s="1">
+        <v>3</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>103</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I20" t="s">
-        <v>177</v>
-      </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1">
+        <v>4</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>105</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H21" t="s">
-        <v>177</v>
-      </c>
-      <c r="I21" t="s">
-        <v>177</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="b">
+      <c r="J21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O21" s="1">
+        <v>3</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>107</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H22" t="s">
-        <v>177</v>
-      </c>
-      <c r="I22" t="s">
-        <v>177</v>
-      </c>
-      <c r="J22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
+        <v>3</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1">
+        <v>4</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
         <v>111</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J24" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1">
+        <v>3</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" t="s">
-        <v>183</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H25" t="s">
-        <v>177</v>
-      </c>
-      <c r="I25" t="s">
-        <v>177</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="b">
+      <c r="J25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O25" s="1">
+        <v>3</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="C26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H26" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" t="s">
-        <v>177</v>
-      </c>
-      <c r="J26" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="b">
+      <c r="J26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O26" s="1">
+        <v>3</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G27" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="I27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I27" t="s">
+      <c r="K27" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J27" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
+        <v>4</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I28" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
+        <v>3</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>115</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H29" t="s">
-        <v>177</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="J29" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" t="b">
+      <c r="L29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O29" s="1">
+        <v>2</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
         <v>117</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D30" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I30" t="s">
-        <v>177</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="b">
+      <c r="K30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
         <v>119</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I31" t="s">
-        <v>177</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="b">
+      <c r="K31" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O31" s="1">
+        <v>3</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D32" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G32" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
+        <v>3</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G33" t="s">
-        <v>71</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I33" t="s">
+      <c r="K33" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J33" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1">
+        <v>4</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
         <v>125</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H34" t="s">
-        <v>177</v>
-      </c>
-      <c r="I34" t="s">
-        <v>177</v>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H35" t="s">
-        <v>177</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="J35" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J35" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1">
+        <v>2</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36" t="s">
         <v>129</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D36" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I36" t="s">
-        <v>177</v>
-      </c>
-      <c r="J36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K36" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37" t="s">
         <v>131</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E37" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I37" t="s">
-        <v>177</v>
-      </c>
-      <c r="J37" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K37" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1">
+        <v>2</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I38" t="s">
-        <v>177</v>
-      </c>
-      <c r="J38" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>3</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39" t="s">
         <v>135</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I39" t="s">
-        <v>177</v>
-      </c>
-      <c r="J39" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K39" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1">
+        <v>4</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40" t="s">
         <v>137</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D40" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I40" t="s">
-        <v>177</v>
-      </c>
-      <c r="J40" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K40" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="1">
+        <v>3</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>139</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D41" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I41" t="s">
-        <v>177</v>
-      </c>
-      <c r="J41" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K41" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1">
+        <v>4</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>141</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D42" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" t="s">
-        <v>72</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I42" t="s">
-        <v>177</v>
-      </c>
-      <c r="J42" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K42" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="1">
+        <v>3</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>143</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G43" t="s">
-        <v>181</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J43" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" s="1">
+        <v>4</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D44" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G44" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I44" t="s">
-        <v>177</v>
-      </c>
-      <c r="J44" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K44" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="1">
+        <v>4</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45" t="s">
         <v>147</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D45" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" t="s">
-        <v>72</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G45" t="s">
+      <c r="I45" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I45" t="s">
-        <v>177</v>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" t="b">
-        <v>1</v>
-      </c>
-      <c r="L45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K45" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" s="1">
+        <v>3</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D46" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" t="s">
-        <v>72</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I46" t="s">
-        <v>177</v>
-      </c>
-      <c r="J46" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K46" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" s="1">
+        <v>4</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47" t="s">
         <v>151</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D47" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G47" t="s">
+      <c r="I47" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I47" t="s">
-        <v>177</v>
-      </c>
-      <c r="J47" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K47" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" s="1">
+        <v>3</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48" t="s">
         <v>153</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I48" t="s">
-        <v>177</v>
-      </c>
-      <c r="J48" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1">
+        <v>4</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49" t="s">
         <v>155</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D49" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" t="s">
-        <v>72</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G49" t="s">
+      <c r="I49" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I49" t="s">
-        <v>177</v>
-      </c>
-      <c r="J49" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K49" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" s="1">
+        <v>3</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>157</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D50" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" t="s">
-        <v>72</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I50" t="s">
-        <v>177</v>
-      </c>
-      <c r="J50" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K50" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1">
+        <v>4</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>56</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D51" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" t="s">
-        <v>72</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I51" t="s">
-        <v>177</v>
-      </c>
-      <c r="J51" t="b">
-        <v>1</v>
-      </c>
-      <c r="K51" t="b">
-        <v>1</v>
-      </c>
-      <c r="L51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" s="1">
+        <v>5</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52" t="s">
         <v>160</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D52" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" t="s">
-        <v>72</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G52" t="s">
+      <c r="I52" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I52" t="s">
-        <v>177</v>
-      </c>
-      <c r="J52" t="b">
-        <v>1</v>
-      </c>
-      <c r="K52" t="b">
-        <v>1</v>
-      </c>
-      <c r="L52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K52" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" s="1">
+        <v>4</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53" t="s">
         <v>162</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D53" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" t="s">
-        <v>72</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G53" t="s">
-        <v>71</v>
-      </c>
-      <c r="J53" t="b">
-        <v>1</v>
-      </c>
-      <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1">
+        <v>4</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54" t="s">
         <v>164</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D54" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" t="s">
-        <v>72</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G54" t="s">
+      <c r="I54" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I54" t="s">
-        <v>177</v>
-      </c>
-      <c r="J54" t="b">
-        <v>1</v>
-      </c>
-      <c r="K54" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K54" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" s="1">
+        <v>5</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
         <v>166</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D55" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G55" t="s">
-        <v>71</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J55" t="b">
-        <v>1</v>
-      </c>
-      <c r="K55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55" s="1">
+        <v>4</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>168</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D56" t="s">
-        <v>71</v>
-      </c>
-      <c r="E56" t="s">
-        <v>72</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G56" t="s">
+      <c r="I56" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H56" t="s">
+      <c r="J56" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I56" t="s">
-        <v>177</v>
-      </c>
-      <c r="J56" t="b">
-        <v>1</v>
-      </c>
-      <c r="K56" t="b">
-        <v>1</v>
-      </c>
-      <c r="L56" t="b">
+      <c r="K56" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O56" s="1">
+        <v>5</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
       <c r="B57" t="s">
         <v>170</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D57" t="s">
-        <v>71</v>
-      </c>
-      <c r="E57" t="s">
-        <v>72</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G57" t="s">
+      <c r="I57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H57" t="s">
+      <c r="J57" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I57" t="s">
-        <v>177</v>
-      </c>
-      <c r="J57" t="b">
-        <v>1</v>
-      </c>
-      <c r="K57" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" t="b">
+      <c r="K57" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O57" s="1">
+        <v>5</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
       <c r="B58" t="s">
         <v>172</v>
       </c>
-      <c r="C58" t="s">
-        <v>186</v>
-      </c>
-      <c r="D58" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" t="s">
-        <v>72</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G58" t="s">
+      <c r="I58" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H58" t="s">
+      <c r="J58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I58" t="s">
-        <v>177</v>
-      </c>
-      <c r="J58" t="b">
-        <v>1</v>
-      </c>
-      <c r="K58" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" t="b">
+      <c r="K58" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O58" s="1">
+        <v>5</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>173</v>
       </c>
-      <c r="C59" t="s">
-        <v>187</v>
-      </c>
-      <c r="D59" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" t="s">
-        <v>72</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="C59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G59" t="s">
+      <c r="I59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H59" t="s">
+      <c r="J59" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I59" t="s">
-        <v>177</v>
-      </c>
-      <c r="J59" t="b">
-        <v>1</v>
-      </c>
-      <c r="K59" t="b">
-        <v>1</v>
-      </c>
-      <c r="L59" t="b">
+      <c r="K59" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O59" s="1">
+        <v>5</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
       <c r="B60" t="s">
         <v>174</v>
       </c>
-      <c r="C60" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" t="s">
-        <v>72</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="C60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G60" t="s">
+      <c r="I60" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H60" t="s">
+      <c r="J60" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I60" t="s">
-        <v>177</v>
-      </c>
-      <c r="J60" t="b">
-        <v>1</v>
-      </c>
-      <c r="K60" t="b">
-        <v>1</v>
-      </c>
-      <c r="L60" t="b">
+      <c r="K60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O60" s="1">
+        <v>5</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
       <c r="B61" t="s">
         <v>175</v>
       </c>
-      <c r="C61" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" t="s">
-        <v>71</v>
-      </c>
-      <c r="E61" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="C61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G61" t="s">
+      <c r="I61" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H61" t="s">
+      <c r="J61" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I61" t="s">
-        <v>177</v>
-      </c>
-      <c r="J61" t="b">
-        <v>1</v>
-      </c>
-      <c r="K61" t="b">
-        <v>1</v>
-      </c>
-      <c r="L61" t="b">
+      <c r="K61" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="O61" s="1">
+        <v>5</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G62" t="s">
-        <v>71</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="I62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J62" t="b">
+      <c r="L62" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="K62" t="b">
+      <c r="M62" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L62" t="b">
+      <c r="N62" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>5</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/measurementInfo.xlsx
+++ b/measurementInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notandi\Desktop\Measurements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4C67ED-35B4-4A96-9FA3-AF678443859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC48EC8-2C23-4429-A402-859E49B48366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="3135" windowWidth="14610" windowHeight="15585" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
+    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{CE7ABF46-5BCF-44D0-B551-448571CF2DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="198">
   <si>
     <t>title</t>
   </si>
@@ -624,6 +624,12 @@
   </si>
   <si>
     <t>IDP Key</t>
+  </si>
+  <si>
+    <t>Most popular</t>
+  </si>
+  <si>
+    <t>Goal</t>
   </si>
 </sst>
 </file>
@@ -659,8 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -996,3085 +1001,3359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204655E-E80D-446C-AF0B-3E0CCA1683CF}">
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>192</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>191</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>193</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>194</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>196</v>
+      </c>
+      <c r="R1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>179</v>
       </c>
-      <c r="L2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1">
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>190</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" t="s">
         <v>124</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>179</v>
       </c>
-      <c r="L3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="1">
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3">
         <v>3</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>183</v>
       </c>
       <c r="B4" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="I4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" t="s">
         <v>124</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>179</v>
       </c>
-      <c r="L4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4">
         <v>3</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" t="s">
         <v>81</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="I5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" t="s">
         <v>124</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>179</v>
       </c>
-      <c r="L5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5">
         <v>3</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" t="s">
         <v>124</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>179</v>
       </c>
-      <c r="L6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1">
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="J7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" t="s">
+        <v>177</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7">
         <v>4</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>86</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>178</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="K8" t="s">
+        <v>177</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="J9" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9">
         <v>3</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s">
         <v>81</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>124</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>178</v>
       </c>
-      <c r="L10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" t="s">
         <v>178</v>
       </c>
-      <c r="L11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11">
         <v>2</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>124</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="K12" t="s">
+        <v>177</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12">
         <v>5</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="I13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s">
         <v>124</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
+      <c r="K13" t="s">
+        <v>177</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13">
         <v>3</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="I14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" t="s">
         <v>124</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
+      <c r="K14" t="s">
+        <v>177</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14">
         <v>3</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>86</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>178</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>178</v>
       </c>
-      <c r="L15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15">
         <v>2</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>178</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>178</v>
       </c>
-      <c r="L16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="1">
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16">
         <v>4</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>91</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="J17" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" t="s">
+        <v>177</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17">
         <v>3</v>
       </c>
-      <c r="P17" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>91</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>178</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>178</v>
       </c>
-      <c r="L18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" s="1" t="b">
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
         <v>0</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18">
         <v>2</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" s="1" t="b">
+      <c r="J19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" t="s">
+        <v>177</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19">
         <v>3</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" t="s">
         <v>84</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>91</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>178</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L20" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="1">
+      <c r="K20" t="s">
+        <v>177</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20">
         <v>4</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>91</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L21" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" s="1" t="b">
+      <c r="J21" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" t="s">
+        <v>177</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
         <v>0</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O21">
         <v>3</v>
       </c>
-      <c r="P21" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>108</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="F22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" t="s">
         <v>81</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="1">
+      <c r="J22" t="s">
+        <v>177</v>
+      </c>
+      <c r="K22" t="s">
+        <v>177</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22">
         <v>3</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P22" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>91</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>178</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>178</v>
       </c>
-      <c r="L23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23">
         <v>4</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>91</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>178</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>178</v>
       </c>
-      <c r="L24" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24">
         <v>3</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>182</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>91</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L25" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N25" s="1" t="b">
+      <c r="J25" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="b">
         <v>0</v>
       </c>
-      <c r="O25" s="1">
+      <c r="O25">
         <v>3</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>181</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>91</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N26" s="1" t="b">
+      <c r="J26" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
         <v>0</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O26">
         <v>3</v>
       </c>
-      <c r="P26" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" t="s">
         <v>84</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>86</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>178</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>178</v>
       </c>
-      <c r="L27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="1">
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27">
         <v>4</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P27" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>76</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="F28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>91</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>124</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L28" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="K28" t="s">
+        <v>177</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28">
         <v>3</v>
       </c>
-      <c r="P28" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P28" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>71</v>
+      </c>
+      <c r="R28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="F29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" t="s">
         <v>84</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>86</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="J29" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" t="s">
         <v>178</v>
       </c>
-      <c r="L29" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N29" s="1" t="b">
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
         <v>0</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O29">
         <v>2</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="F30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" t="s">
         <v>81</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>91</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>124</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L30" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" s="1" t="b">
+      <c r="K30" t="s">
+        <v>177</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
         <v>0</v>
       </c>
-      <c r="O30" s="1">
-        <v>1</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
         <v>119</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>120</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>91</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>124</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L31" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N31" s="1" t="b">
+      <c r="K31" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="b">
         <v>0</v>
       </c>
-      <c r="O31" s="1">
+      <c r="O31">
         <v>3</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P31" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="F32" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>178</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>178</v>
       </c>
-      <c r="L32" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" s="1">
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32">
         <v>3</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>76</v>
+      </c>
+      <c r="R32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="1" t="s">
+      <c r="I33" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" t="s">
         <v>124</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" t="s">
         <v>146</v>
       </c>
-      <c r="L33" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N33" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="1">
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33">
         <v>4</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" t="s">
         <v>81</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" t="s">
         <v>86</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="1">
-        <v>1</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J34" t="s">
+        <v>177</v>
+      </c>
+      <c r="K34" t="s">
+        <v>177</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>71</v>
+      </c>
+      <c r="R34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>86</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="J35" t="s">
+        <v>177</v>
+      </c>
+      <c r="K35" t="s">
         <v>178</v>
       </c>
-      <c r="L35" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O35" s="1">
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35">
         <v>2</v>
       </c>
-      <c r="P35" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P35" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>76</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="F36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" t="s">
         <v>81</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>91</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>124</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L36" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" s="1">
-        <v>1</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>177</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>71</v>
+      </c>
+      <c r="R36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="F37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>91</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>124</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L37" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="1">
+      <c r="K37" t="s">
+        <v>177</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37">
         <v>2</v>
       </c>
-      <c r="P37" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P37" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>71</v>
+      </c>
+      <c r="R37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>134</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="F38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" t="s">
         <v>81</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>91</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L38" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="J38" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" t="s">
+        <v>177</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38">
         <v>3</v>
       </c>
-      <c r="P38" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>135</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" t="s">
         <v>136</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="F39" t="s">
+        <v>71</v>
+      </c>
+      <c r="G39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" t="s">
         <v>73</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>91</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>124</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L39" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" s="1">
+      <c r="K39" t="s">
+        <v>177</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39">
         <v>4</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P39" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>71</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>137</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" t="s">
         <v>138</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="F40" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" t="s">
         <v>81</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>91</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>124</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L40" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" s="1">
+      <c r="K40" t="s">
+        <v>177</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40">
         <v>3</v>
       </c>
-      <c r="P40" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P40" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>71</v>
+      </c>
+      <c r="R40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>139</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" t="s">
         <v>140</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="F41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" t="s">
         <v>73</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>91</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>124</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L41" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N41" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" s="1">
+      <c r="K41" t="s">
+        <v>177</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41">
         <v>4</v>
       </c>
-      <c r="P41" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P41" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" t="s">
         <v>142</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="F42" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" t="s">
         <v>81</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>86</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>124</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L42" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N42" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" s="1">
+      <c r="K42" t="s">
+        <v>177</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42">
         <v>3</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P42" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>76</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>143</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" t="s">
         <v>144</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="F43" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" t="s">
         <v>86</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>124</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" t="s">
         <v>178</v>
       </c>
-      <c r="L43" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N43" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" s="1">
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43">
         <v>4</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P43" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>76</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
+      <c r="E44" t="s">
         <v>145</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="F44" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" t="s">
         <v>146</v>
       </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J44" s="1" t="s">
+      <c r="I44" t="s">
+        <v>71</v>
+      </c>
+      <c r="J44" t="s">
         <v>124</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O44" s="1">
+      <c r="K44" t="s">
+        <v>177</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44">
         <v>4</v>
       </c>
-      <c r="P44" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P44" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>147</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" t="s">
         <v>148</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="F45" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" t="s">
         <v>81</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" t="s">
         <v>91</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>124</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L45" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O45" s="1">
+      <c r="K45" t="s">
+        <v>177</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45">
         <v>3</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P45" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>71</v>
+      </c>
+      <c r="R45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>149</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" t="s">
         <v>150</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H46" s="1" t="s">
+      <c r="F46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" t="s">
         <v>73</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" t="s">
         <v>91</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>124</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L46" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N46" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" s="1">
+      <c r="K46" t="s">
+        <v>177</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46">
         <v>4</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P46" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>71</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47" t="s">
         <v>151</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>151</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" t="s">
         <v>152</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="F47" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s">
+        <v>72</v>
+      </c>
+      <c r="H47" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" t="s">
         <v>91</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" t="s">
         <v>124</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L47" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N47" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O47" s="1">
+      <c r="K47" t="s">
+        <v>177</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47">
         <v>3</v>
       </c>
-      <c r="P47" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P47" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>71</v>
+      </c>
+      <c r="R47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48" t="s">
         <v>153</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>53</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="F48" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" t="s">
+        <v>72</v>
+      </c>
+      <c r="H48" t="s">
         <v>73</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" t="s">
         <v>86</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>124</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L48" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N48" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O48" s="1">
+      <c r="K48" t="s">
+        <v>177</v>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48">
         <v>4</v>
       </c>
-      <c r="P48" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P48" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>71</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>155</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="F49" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s">
+        <v>72</v>
+      </c>
+      <c r="H49" t="s">
         <v>81</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" t="s">
         <v>91</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>124</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L49" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O49" s="1">
+      <c r="K49" t="s">
+        <v>177</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49">
         <v>3</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P49" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>71</v>
+      </c>
+      <c r="R49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>157</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
         <v>158</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H50" s="1" t="s">
+      <c r="F50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G50" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50" t="s">
         <v>73</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" t="s">
         <v>91</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>124</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L50" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N50" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O50" s="1">
+      <c r="K50" t="s">
+        <v>177</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50">
         <v>4</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P50" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>71</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>56</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" t="s">
         <v>159</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="F51" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51" t="s">
+        <v>72</v>
+      </c>
+      <c r="H51" t="s">
         <v>84</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" t="s">
         <v>91</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" t="s">
         <v>124</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L51" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N51" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O51" s="1">
+      <c r="K51" t="s">
+        <v>177</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51">
         <v>5</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P51" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>57</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" t="s">
         <v>161</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="F52" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" t="s">
+        <v>72</v>
+      </c>
+      <c r="H52" t="s">
         <v>73</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" t="s">
         <v>91</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>124</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L52" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N52" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O52" s="1">
+      <c r="K52" t="s">
+        <v>177</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52">
         <v>4</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P52" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>162</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" t="s">
         <v>163</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H53" s="1" t="s">
+      <c r="F53" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H53" t="s">
         <v>81</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N53" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O53" s="1">
+      <c r="I53" t="s">
+        <v>71</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53">
         <v>4</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P53" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>164</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" t="s">
         <v>165</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="F54" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" t="s">
+        <v>72</v>
+      </c>
+      <c r="H54" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" t="s">
         <v>91</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>124</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L54" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N54" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O54" s="1">
+      <c r="K54" t="s">
+        <v>177</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54">
         <v>5</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P54" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
         <v>166</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" t="s">
         <v>166</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" t="s">
         <v>167</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="F55" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" t="s">
         <v>146</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" t="s">
         <v>73</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J55" s="1" t="s">
+      <c r="I55" t="s">
+        <v>71</v>
+      </c>
+      <c r="J55" t="s">
         <v>124</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" t="s">
         <v>180</v>
       </c>
-      <c r="L55" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N55" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O55" s="1">
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55">
         <v>4</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P55" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>168</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>62</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" t="s">
         <v>168</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" t="s">
         <v>169</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="F56" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" t="s">
         <v>61</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" t="s">
         <v>91</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>124</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L56" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N56" s="1" t="b">
+      <c r="K56" t="s">
+        <v>177</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
         <v>0</v>
       </c>
-      <c r="O56" s="1">
+      <c r="O56">
         <v>5</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P56" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
       <c r="B57" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>63</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" t="s">
         <v>170</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" t="s">
         <v>171</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="F57" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57" t="s">
+        <v>72</v>
+      </c>
+      <c r="H57" t="s">
         <v>61</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" t="s">
         <v>91</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>124</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L57" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M57" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N57" s="1" t="b">
+      <c r="K57" t="s">
+        <v>177</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
         <v>0</v>
       </c>
-      <c r="O57" s="1">
+      <c r="O57">
         <v>5</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P57" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
       <c r="B58" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>64</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" t="s">
         <v>172</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" t="s">
         <v>185</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58" t="s">
         <v>61</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" t="s">
         <v>91</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>124</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L58" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M58" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N58" s="1" t="b">
+      <c r="K58" t="s">
+        <v>177</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="b">
         <v>0</v>
       </c>
-      <c r="O58" s="1">
+      <c r="O58">
         <v>5</v>
       </c>
-      <c r="P58" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P58" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>173</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>173</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" t="s">
         <v>186</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="F59" t="s">
+        <v>71</v>
+      </c>
+      <c r="G59" t="s">
+        <v>72</v>
+      </c>
+      <c r="H59" t="s">
         <v>61</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" t="s">
         <v>91</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>124</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L59" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M59" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N59" s="1" t="b">
+      <c r="K59" t="s">
+        <v>177</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
         <v>0</v>
       </c>
-      <c r="O59" s="1">
+      <c r="O59">
         <v>5</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P59" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
       <c r="B60" t="s">
         <v>174</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>66</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" t="s">
         <v>174</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" t="s">
         <v>187</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="F60" t="s">
+        <v>71</v>
+      </c>
+      <c r="G60" t="s">
+        <v>72</v>
+      </c>
+      <c r="H60" t="s">
         <v>61</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" t="s">
         <v>86</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>124</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N60" s="1" t="b">
+      <c r="K60" t="s">
+        <v>177</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
         <v>0</v>
       </c>
-      <c r="O60" s="1">
+      <c r="O60">
         <v>5</v>
       </c>
-      <c r="P60" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P60" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
       <c r="B61" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>67</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" t="s">
         <v>188</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H61" s="1" t="s">
+      <c r="F61" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" t="s">
+        <v>72</v>
+      </c>
+      <c r="H61" t="s">
         <v>61</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" t="s">
         <v>91</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" t="s">
         <v>124</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L61" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M61" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N61" s="1" t="b">
+      <c r="K61" t="s">
+        <v>177</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
         <v>0</v>
       </c>
-      <c r="O61" s="1">
+      <c r="O61">
         <v>5</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P61" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1" t="s">
+      <c r="E62" t="s">
         <v>176</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
+      <c r="G62" t="s">
         <v>146</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" t="s">
         <v>73</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J62" s="1" t="s">
+      <c r="I62" t="s">
+        <v>71</v>
+      </c>
+      <c r="J62" t="s">
         <v>124</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" t="s">
         <v>180</v>
       </c>
-      <c r="L62" s="1" t="b">
+      <c r="L62" t="b">
         <v>0</v>
       </c>
-      <c r="M62" s="1" t="b">
+      <c r="M62" t="b">
         <v>0</v>
       </c>
-      <c r="N62" s="1" t="b">
+      <c r="N62" t="b">
         <v>0</v>
       </c>
-      <c r="O62" s="1">
+      <c r="O62">
         <v>5</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="P62" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q62" t="s">
         <v>71</v>
       </c>
     </row>
